--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf3205aa02f2a4aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb1f1c72adea54e16"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -316,7 +316,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>已脱敏的多语言登录页发布材料，包含页面、页面脚本、语言包、认证场景和待完成Playwright脚本。</x:v>
+        <x:v>本次多语言登录页发布业务数据，包含登录页面、页面脚本、语言包、认证场景和待完成Playwright脚本。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="108" customHeight="1">
@@ -329,88 +329,88 @@
     </x:row>
     <x:row r="7" ht="108" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
+        <x:v>为登录团队和发布经理复核通行密钥成功、异常后密码降级、多语言错误提示、错误后焦点与键盘路径，形成放量决策资料。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="108" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>output/release_readiness.json、output/reports/auth_flow_matrix.csv、output/reports/focus_recovery.csv、output/reports/locale_copy_findings.csv、output/tests/login-webauthn-fallback.spec.ts</x:v>
+        <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="108" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>目标输出文件</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>材料核对→本地页面服务→认证场景驱动→虚拟凭据→密码降级→多语言文案观察→焦点恢复→Tab键序列→发布就绪摘要</x:v>
+        <x:v>output/release_readiness.json、output/reports/auth_flow_matrix.csv、output/reports/focus_recovery.csv、output/reports/locale_copy_findings.csv、output/tests/login-webauthn-fallback.spec.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>通行密钥路径</x:v>
+        <x:v>业务操作链</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；不支持路径由addInitScript呈现能力边界。</x:v>
+        <x:v>材料核对→本地页面服务→认证场景驱动→虚拟凭据→密码降级→多语言文案观察→焦点恢复→Tab键序列→发布就绪摘要</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="108" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>本地化文案观察</x:v>
+        <x:v>通行密钥路径</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>按locale和copy_key在页面中触发错误，将语言包全文与错误元素innerText写入文案表。</x:v>
+        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；不支持路径由addInitScript呈现能力边界。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="108" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>键盘与焦点观察</x:v>
+        <x:v>本地化文案观察</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
+        <x:v>按locale和copy_key在页面中触发错误，将语言包全文与错误元素innerText写入文案表。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="108" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>发布结论归纳</x:v>
+        <x:v>键盘与焦点观察</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>从认证路径、本地化文案和焦点恢复三份CSV统计观察数，归纳blockers并给出release_decision。</x:v>
+        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="108" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>Playwright软件步骤</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>五个业务交付路径齐全，场景路径、显示文案、错误后焦点、Tab键序列和发布结论彼此闭合。</x:v>
+        <x:v>脚本启动只提供app目录的本地HTTP服务；Playwright依次打开场景页面、配置BrowserContext凭据、执行locator与键盘操作，再从页面实际状态写出三份CSV和发布摘要。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="108" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>场景主键、通行密钥成功状态、密码表单状态、页面语言、完整错误文案、活动焦点、Tab键序列与发布摘要。</x:v>
+        <x:v>完成Playwright脚本、认证场景矩阵、本地化文案观察、焦点恢复表和发布就绪摘要五项交付，路径、场景主键、显示文案、焦点与发布结论彼此闭合。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="108" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>辅助函数名、test分组方式、HTTP路由函数名、CSV引号形式、JSON非语义键序、日志措辞和Playwright补丁版本。</x:v>
+        <x:v>允许重组test分组、辅助函数、HTTP路由和报表函数；不得改变输入主键、场景含义、页面观察值、固定交付路径或下游字段合同。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R446af9ccd9534d85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2479d15509c6495b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb1f1c72adea54e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ra0cfd67c9ad74861"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -329,79 +329,79 @@
     </x:row>
     <x:row r="7" ht="108" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>业务目标</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>为登录团队和发布经理复核通行密钥成功、异常后密码降级、多语言错误提示、错误后焦点与键盘路径，形成放量决策资料。</x:v>
+        <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="108" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>目标输出文件</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
+        <x:v>output/release_readiness.json、output/reports/auth_flow_matrix.csv、output/reports/focus_recovery.csv、output/reports/locale_copy_findings.csv、output/tests/login-webauthn-fallback.spec.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="108" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>核心操作链</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>output/release_readiness.json、output/reports/auth_flow_matrix.csv、output/reports/focus_recovery.csv、output/reports/locale_copy_findings.csv、output/tests/login-webauthn-fallback.spec.ts</x:v>
+        <x:v>登录团队材料核对→本地页面服务→认证场景驱动→虚拟凭据→密码降级→多语言文案观察→焦点恢复→Tab键序列→发布经理放量摘要</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>业务操作链</x:v>
+        <x:v>通行密钥路径</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>材料核对→本地页面服务→认证场景驱动→虚拟凭据→密码降级→多语言文案观察→焦点恢复→Tab键序列→发布就绪摘要</x:v>
+        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；不支持路径由addInitScript呈现能力边界。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="108" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>通行密钥路径</x:v>
+        <x:v>本地化文案观察</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；不支持路径由addInitScript呈现能力边界。</x:v>
+        <x:v>按locale和copy_key在页面中触发错误，将语言包全文与错误元素innerText写入文案表。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="108" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>本地化文案观察</x:v>
+        <x:v>键盘与焦点观察</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>按locale和copy_key在页面中触发错误，将语言包全文与错误元素innerText写入文案表。</x:v>
+        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="108" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>键盘与焦点观察</x:v>
+        <x:v>Playwright软件步骤</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
+        <x:v>脚本启动只提供app目录的本地HTTP服务；Playwright依次打开场景页面、配置BrowserContext凭据、执行locator与键盘操作，再从页面实际状态写出三份CSV和发布摘要。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="108" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>Playwright软件步骤</x:v>
+        <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>脚本启动只提供app目录的本地HTTP服务；Playwright依次打开场景页面、配置BrowserContext凭据、执行locator与键盘操作，再从页面实际状态写出三份CSV和发布摘要。</x:v>
+        <x:v>完成Playwright脚本、认证场景矩阵、本地化文案观察、焦点恢复表和发布就绪摘要五项交付，路径、场景主键、显示文案、焦点与发布结论彼此闭合。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="108" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>交付要求</x:v>
+        <x:v>可验证点</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>完成Playwright脚本、认证场景矩阵、本地化文案观察、焦点恢复表和发布就绪摘要五项交付，路径、场景主键、显示文案、焦点与发布结论彼此闭合。</x:v>
+        <x:v>场景主键、通行密钥成功状态、密码表单状态、页面语言、完整错误文案、活动焦点、Tab键序列与发布摘要。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="108" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>实现边界</x:v>
+        <x:v>不适合作为评分点的内容</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
         <x:v>允许重组test分组、辅助函数、HTTP路由和报表函数；不得改变输入主键、场景含义、页面观察值、固定交付路径或下游字段合同。</x:v>
@@ -410,7 +410,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2479d15509c6495b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56c6937f9a214d52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ra0cfd67c9ad74861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Redddb68bf4df4c5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table" displayName="Table" ref="A1:B16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table" displayName="Table" ref="A1:B15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="模块"/>
     <x:tableColumn id="2" name="规格内容"/>
@@ -313,26 +313,26 @@
     </x:row>
     <x:row r="5" ht="108" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>输入来源</x:v>
+        <x:v>业务输入</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>本次多语言登录页发布业务数据，包含登录页面、页面脚本、语言包、认证场景和待完成Playwright脚本。</x:v>
+        <x:v>本次多语言登录页发布输入包含登录页面、页面脚本、语言包、认证场景和待完成Playwright脚本。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="108" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>解压输入数据包.zip，阅读README.md，在starter/login-webauthn-fallback.spec.ts完成脚本，再从input_data执行npm run process。</x:v>
+        <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="108" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>发布目标</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
+        <x:v>检查通行密钥成功、能力降级、密码恢复、多语言提示和错误后键盘焦点，给发布经理提供放量依据。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="108" customHeight="1">
@@ -345,72 +345,64 @@
     </x:row>
     <x:row r="9" ht="108" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>通行密钥路径</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>登录团队材料核对→本地页面服务→认证场景驱动→虚拟凭据→密码降级→多语言文案观察→焦点恢复→Tab键序列→发布经理放量摘要</x:v>
+        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；能力降级路径由addInitScript呈现浏览器状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>通行密钥路径</x:v>
+        <x:v>本地化文案</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；不支持路径由addInitScript呈现能力边界。</x:v>
+        <x:v>按locale和copy_key触发页面错误，将语言包全文与错误元素innerText写入文案表。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="108" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>本地化文案观察</x:v>
+        <x:v>键盘与焦点</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>按locale和copy_key在页面中触发错误，将语言包全文与错误元素innerText写入文案表。</x:v>
+        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="108" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>键盘与焦点观察</x:v>
+        <x:v>Playwright步骤</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
+        <x:v>脚本启动只提供app目录的本地HTTP服务；Playwright依次打开场景页面、配置BrowserContext凭据、执行locator与键盘操作，再从页面实际状态写出三份CSV和发布摘要。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="108" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>Playwright软件步骤</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>脚本启动只提供app目录的本地HTTP服务；Playwright依次打开场景页面、配置BrowserContext凭据、执行locator与键盘操作，再从页面实际状态写出三份CSV和发布摘要。</x:v>
+        <x:v>交付完成的Playwright脚本、认证场景矩阵、本地化文案观察、焦点恢复表和发布就绪摘要，供登录团队及各审查角色继续使用。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="108" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>结果对账</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>完成Playwright脚本、认证场景矩阵、本地化文案观察、焦点恢复表和发布就绪摘要五项交付，路径、场景主键、显示文案、焦点与发布结论彼此闭合。</x:v>
+        <x:v>场景主键、路径、显示文案、活动焦点和键盘序列在输入、业务表与发布摘要之间保持一致。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="108" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>场景主键、通行密钥成功状态、密码表单状态、页面语言、完整错误文案、活动焦点、Tab键序列与发布摘要。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="108" customHeight="1">
-      <x:c r="A16" s="7" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B16" s="7" t="str">
-        <x:v>允许重组test分组、辅助函数、HTTP路由和报表函数；不得改变输入主键、场景含义、页面观察值、固定交付路径或下游字段合同。</x:v>
+        <x:v>允许调整test分组、辅助函数、HTTP路由和报表函数；输入主键、场景含义、页面观察值、固定交付路径和下游字段合同保持不变。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56c6937f9a214d52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3962542338a3428b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Redddb68bf4df4c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf316e1bab71d47df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table" displayName="Table" ref="A1:B15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table" displayName="Table" ref="A1:B16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="模块"/>
     <x:tableColumn id="2" name="规格内容"/>
@@ -305,10 +305,10 @@
     </x:row>
     <x:row r="4" ht="108" customHeight="1">
       <x:c r="A4" s="7" t="str">
-        <x:v>辅助工具</x:v>
+        <x:v>业务角色</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Node.js20以上与npm负责启动本地HTTP服务、Playwright入口及CSV和JSON导出；PowerShell或系统终端负责启动。</x:v>
+        <x:v>登录团队维护认证脚本，认证产品经理、本地化编辑和可访问性专员分别读取三份观察表，发布经理使用就绪摘要决定是否放量。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="108" customHeight="1">
@@ -321,7 +321,7 @@
     </x:row>
     <x:row r="6" ht="108" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>输入文件</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>input_data/README.md、input_data/app/locales/en-US.json、input_data/app/locales/es-ES.json、input_data/app/locales/zh-CN.json、input_data/app/login.html、input_data/app/login.js、input_data/package.json、input_data/playwright.config.cjs、input_data/scenarios/auth_scenarios.json、input_data/starter/login-webauthn-fallback.spec.ts、input_data/tools/run-task.mjs</x:v>
@@ -329,80 +329,88 @@
     </x:row>
     <x:row r="7" ht="108" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>发布目标</x:v>
+        <x:v>发布判断</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>检查通行密钥成功、能力降级、密码恢复、多语言提示和错误后键盘焦点，给发布经理提供放量依据。</x:v>
+        <x:v>观察通行密钥成功、能力降级、密码恢复、多语言提示和错误后键盘焦点，为灰度窗口提供放量依据。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="108" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>本地页面服务</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>output/release_readiness.json、output/reports/auth_flow_matrix.csv、output/reports/focus_recovery.csv、output/reports/locale_copy_findings.csv、output/tests/login-webauthn-fallback.spec.ts</x:v>
+        <x:v>Node.js提供app目录中的登录页、页面脚本和语言文件，页面只通过本机回环地址访问。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="108" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>通行密钥路径</x:v>
+        <x:v>认证场景编排</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据，页面完成navigator.credentials.get；能力降级路径由addInitScript呈现浏览器状态。</x:v>
+        <x:v>Playwright按scenario_id读取locale、webauthn_mode、预期路径、错误文案键、焦点目标和Tab次数。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>本地化文案</x:v>
+        <x:v>通行密钥交互</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>按locale和copy_key触发页面错误，将语言包全文与错误元素innerText写入文案表。</x:v>
+        <x:v>成功路径在BrowserContext中安装与127.0.0.1匹配的虚拟凭据并调用navigator.credentials.get；能力降级路径由addInitScript呈现浏览器状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="108" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>键盘与焦点</x:v>
+        <x:v>多语言显示</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
+        <x:v>按locale和copy_key触发页面错误，将语言包全文与错误元素innerText写入文案观察表。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="108" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>Playwright步骤</x:v>
+        <x:v>焦点与键盘</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>脚本启动只提供app目录的本地HTTP服务；Playwright依次打开场景页面、配置BrowserContext凭据、执行locator与键盘操作，再从页面实际状态写出三份CSV和发布摘要。</x:v>
+        <x:v>从document.activeElement读取错误后焦点，按keyboard_tabs逐次发送Tab并保存data-testid序列。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="108" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>交付要求</x:v>
+        <x:v>业务报表</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>交付完成的Playwright脚本、认证场景矩阵、本地化文案观察、焦点恢复表和发布就绪摘要，供登录团队及各审查角色继续使用。</x:v>
+        <x:v>场景矩阵记录认证路径和密码表单状态，文案表记录页面显示，焦点表记录活动元素与键盘序列。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="108" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>结果对账</x:v>
+        <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>场景主键、路径、显示文案、活动焦点和键盘序列在输入、业务表与发布摘要之间保持一致。</x:v>
+        <x:v>从三份业务表汇总场景数量、语言范围、密码降级、阻塞项和release_decision。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="108" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>实现边界</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>允许调整test分组、辅助函数、HTTP路由和报表函数；输入主键、场景含义、页面观察值、固定交付路径和下游字段合同保持不变。</x:v>
+        <x:v>output/release_readiness.json、output/reports/auth_flow_matrix.csv、output/reports/focus_recovery.csv、output/reports/locale_copy_findings.csv、output/tests/login-webauthn-fallback.spec.ts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="108" customHeight="1">
+      <x:c r="A16" s="7" t="str">
+        <x:v>脚本维护</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>test分组、辅助函数、HTTP路由和报表函数可以调整；scenario_id、场景含义、页面观察值和交付路径保持一致。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3962542338a3428b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67c5df2d77794ca0"/>
   </x:tableParts>
 </x:worksheet>
 </file>